--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU 03/HRM/pre LAM_HRM-2031-0160/Panel 02/Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU03_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU 03/HRM/pre LAM_HRM-2031-0160/Panel 02/Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU03_Front_Summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,6 +454,11 @@
           <t>Unit 7</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Pad 1</t>
+        </is>
+      </c>
       <c r="C2" t="n">
         <v>17.05729</v>
       </c>
@@ -483,10 +488,10 @@
         <v>16.98348</v>
       </c>
       <c r="D3" t="n">
+        <v>16.83739</v>
+      </c>
+      <c r="E3" t="n">
         <v>16.90502</v>
-      </c>
-      <c r="E3" t="n">
-        <v>16.83739</v>
       </c>
       <c r="F3" t="n">
         <v>42.85172</v>
@@ -505,13 +510,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.66457</v>
+        <v>17.08919</v>
       </c>
       <c r="D4" t="n">
         <v>16.63428</v>
       </c>
       <c r="E4" t="n">
-        <v>17.08919</v>
+        <v>16.66457</v>
       </c>
       <c r="F4" t="n">
         <v>42.3411</v>
@@ -533,10 +538,10 @@
         <v>16.99914</v>
       </c>
       <c r="D5" t="n">
+        <v>16.83743</v>
+      </c>
+      <c r="E5" t="n">
         <v>16.84484</v>
-      </c>
-      <c r="E5" t="n">
-        <v>16.83743</v>
       </c>
       <c r="F5" t="n">
         <v>43.47677</v>
@@ -555,13 +560,13 @@
         </is>
       </c>
       <c r="C6" t="n">
+        <v>16.99616</v>
+      </c>
+      <c r="D6" t="n">
         <v>16.74517</v>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
         <v>16.77895</v>
-      </c>
-      <c r="E6" t="n">
-        <v>16.99616</v>
       </c>
       <c r="F6" t="n">
         <v>42.73971</v>
@@ -580,13 +585,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.60985</v>
+        <v>16.80425</v>
       </c>
       <c r="D7" t="n">
         <v>16.51808</v>
       </c>
       <c r="E7" t="n">
-        <v>16.80425</v>
+        <v>16.60985</v>
       </c>
       <c r="F7" t="n">
         <v>42.05615</v>
@@ -605,13 +610,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.93156</v>
+        <v>17.09659</v>
       </c>
       <c r="D8" t="n">
         <v>16.51422</v>
       </c>
       <c r="E8" t="n">
-        <v>17.09659</v>
+        <v>16.93156</v>
       </c>
       <c r="F8" t="n">
         <v>43.16577</v>
@@ -630,13 +635,13 @@
         </is>
       </c>
       <c r="C9" t="n">
+        <v>16.77501</v>
+      </c>
+      <c r="D9" t="n">
         <v>16.47349</v>
       </c>
-      <c r="D9" t="n">
+      <c r="E9" t="n">
         <v>16.64679</v>
-      </c>
-      <c r="E9" t="n">
-        <v>16.77501</v>
       </c>
       <c r="F9" t="n">
         <v>42.83001</v>
@@ -767,13 +772,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>16.61856</v>
+        <v>16.98796</v>
       </c>
       <c r="D14" t="n">
         <v>16.52774</v>
       </c>
       <c r="E14" t="n">
-        <v>16.98796</v>
+        <v>16.61856</v>
       </c>
       <c r="F14" t="n">
         <v>41.68782</v>
@@ -795,10 +800,10 @@
         <v>17.01745</v>
       </c>
       <c r="D15" t="n">
+        <v>16.73735</v>
+      </c>
+      <c r="E15" t="n">
         <v>16.78878</v>
-      </c>
-      <c r="E15" t="n">
-        <v>16.73735</v>
       </c>
       <c r="F15" t="n">
         <v>42.68862</v>
@@ -817,13 +822,13 @@
         </is>
       </c>
       <c r="C16" t="n">
+        <v>16.93116</v>
+      </c>
+      <c r="D16" t="n">
+        <v>16.82403</v>
+      </c>
+      <c r="E16" t="n">
         <v>16.86911</v>
-      </c>
-      <c r="D16" t="n">
-        <v>16.93116</v>
-      </c>
-      <c r="E16" t="n">
-        <v>16.82403</v>
       </c>
       <c r="F16" t="n">
         <v>41.97266</v>
@@ -842,13 +847,13 @@
         </is>
       </c>
       <c r="C17" t="n">
+        <v>16.86</v>
+      </c>
+      <c r="D17" t="n">
+        <v>16.6776</v>
+      </c>
+      <c r="E17" t="n">
         <v>16.74781</v>
-      </c>
-      <c r="D17" t="n">
-        <v>16.86</v>
-      </c>
-      <c r="E17" t="n">
-        <v>16.6776</v>
       </c>
       <c r="F17" t="n">
         <v>43.07716</v>
@@ -867,10 +872,10 @@
         </is>
       </c>
       <c r="C18" t="n">
+        <v>16.80025</v>
+      </c>
+      <c r="D18" t="n">
         <v>16.61222</v>
-      </c>
-      <c r="D18" t="n">
-        <v>16.80025</v>
       </c>
       <c r="E18" t="n">
         <v>16.75948</v>
@@ -920,10 +925,10 @@
         <v>17.02993</v>
       </c>
       <c r="D20" t="n">
+        <v>16.79762</v>
+      </c>
+      <c r="E20" t="n">
         <v>16.94462</v>
-      </c>
-      <c r="E20" t="n">
-        <v>16.79762</v>
       </c>
       <c r="F20" t="n">
         <v>42.61317</v>
@@ -938,42 +943,12 @@
     <row r="21">
       <c r="C21" t="inlineStr">
         <is>
-          <t>Rz max</t>
+          <t>Dimple</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Rz mean</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Rz min</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Rz max</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Ra mean</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Ra Std dev</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>Ra min</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>Ra max</t>
+          <t>Bump</t>
         </is>
       </c>
     </row>
@@ -985,32 +960,14 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>roughness</t>
+          <t>via 1</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.7563299999999999</v>
+        <v>0.61324</v>
       </c>
       <c r="D22" t="n">
-        <v>0.08153000000000001</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0.61558</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0.95774</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0.11005</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0.00754</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0.09124</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0.12903</v>
+        <v>1.12099</v>
       </c>
     </row>
     <row r="23">
@@ -1020,28 +977,10 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.75819</v>
+        <v>0.61558</v>
       </c>
       <c r="D23" t="n">
-        <v>0.08079</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0.61281</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0.97816</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0.11299</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0.00753</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0.09273000000000001</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0.12799</v>
+        <v>1.10896</v>
       </c>
     </row>
     <row r="24">
@@ -1051,28 +990,10 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.76611</v>
+        <v>0.6114000000000001</v>
       </c>
       <c r="D24" t="n">
-        <v>0.08007</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0.61818</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0.99442</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0.10744</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0.0076</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0.09259000000000001</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0.12805</v>
+        <v>1.10645</v>
       </c>
     </row>
     <row r="25">
@@ -1082,28 +1003,10 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.73587</v>
+        <v>0.59505</v>
       </c>
       <c r="D25" t="n">
-        <v>0.08047</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0.59287</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0.97973</v>
-      </c>
-      <c r="G25" t="n">
-        <v>0.10977</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0.00762</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0.09265</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0.12759</v>
+        <v>1.13548</v>
       </c>
     </row>
     <row r="26">
@@ -1113,28 +1016,10 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.75357</v>
+        <v>0.61475</v>
       </c>
       <c r="D26" t="n">
-        <v>0.08024000000000001</v>
-      </c>
-      <c r="E26" t="n">
-        <v>0.59661</v>
-      </c>
-      <c r="F26" t="n">
-        <v>0.96416</v>
-      </c>
-      <c r="G26" t="n">
-        <v>0.10901</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0.00745</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0.09263</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0.12703</v>
+        <v>1.11083</v>
       </c>
     </row>
     <row r="27">
@@ -1144,28 +1029,10 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.74918</v>
+        <v>0.61281</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0825</v>
-      </c>
-      <c r="E27" t="n">
-        <v>0.61809</v>
-      </c>
-      <c r="F27" t="n">
-        <v>0.9576</v>
-      </c>
-      <c r="G27" t="n">
-        <v>0.11013</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0.00763</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0.09318</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0.12826</v>
+        <v>1.1326</v>
       </c>
     </row>
     <row r="28">
@@ -1175,28 +1042,10 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.76692</v>
+        <v>0.62775</v>
       </c>
       <c r="D28" t="n">
-        <v>0.08057</v>
-      </c>
-      <c r="E28" t="n">
-        <v>0.59905</v>
-      </c>
-      <c r="F28" t="n">
-        <v>0.97578</v>
-      </c>
-      <c r="G28" t="n">
-        <v>0.10953</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0.00762</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0.09259000000000001</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0.12749</v>
+        <v>1.10394</v>
       </c>
     </row>
     <row r="29">
@@ -1206,28 +1055,10 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.74155</v>
+        <v>0.60473</v>
       </c>
       <c r="D29" t="n">
-        <v>0.08191</v>
-      </c>
-      <c r="E29" t="n">
-        <v>0.60254</v>
-      </c>
-      <c r="F29" t="n">
-        <v>0.96217</v>
-      </c>
-      <c r="G29" t="n">
-        <v>0.10964</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0.00773</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0.09496</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0.12628</v>
+        <v>1.12633</v>
       </c>
     </row>
     <row r="30">
@@ -1237,28 +1068,336 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.7576000000000001</v>
+        <v>0.62117</v>
       </c>
       <c r="D30" t="n">
-        <v>0.08066</v>
-      </c>
-      <c r="E30" t="n">
-        <v>0.61986</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0.98506</v>
-      </c>
-      <c r="G30" t="n">
-        <v>0.1121</v>
-      </c>
-      <c r="H30" t="n">
+        <v>1.1009</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Rz max</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Rz mean</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Rz min</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Rz max</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Ra mean</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Ra Std dev</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Ra min</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Ra max</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>roughness</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>0.7624300000000001</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.08373999999999999</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.5969100000000001</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.96279</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.1087</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.00768</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.09149</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.12574</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>0.7312</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.0825</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.60986</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.96512</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.10876</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.00766</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.09369</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.12538</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>0.73582</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.08119</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.60559</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.94385</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.10874</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.00762</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.09314</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0.1289</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>0.76231</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.08064</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.61183</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.96651</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.10938</v>
+      </c>
+      <c r="H35" t="n">
         <v>0.0077</v>
       </c>
-      <c r="I30" t="n">
-        <v>0.09227</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0.12699</v>
+      <c r="I35" t="n">
+        <v>0.09535</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.12589</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>0.73883</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.08217000000000001</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.6085</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.96551</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.10869</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.00765</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.09218999999999999</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.12798</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>0.74313</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0.08103</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.6091299999999999</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.9792999999999999</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.11148</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.00758</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.09419</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0.12604</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>0.76449</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0.08295</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.6228</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.9747400000000001</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.10832</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.00762</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.09349</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.13003</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>0.77302</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0.08246000000000001</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.60802</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.96918</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.10917</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.00775</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.09389</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.1272</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>0.73082</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0.08141</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.60402</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.9681</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.10976</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.00762</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.09393</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0.12554</v>
       </c>
     </row>
   </sheetData>
